--- a/src/test/resources/testdata/registrationData.xlsx
+++ b/src/test/resources/testdata/registrationData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Loka_KeralamOnline_QA-main\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFAF123B-E70A-4816-B9BE-84B53CFBEBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772A11AC-390D-4ECA-95EB-66A1950FAB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{1CEF1BEB-5E8D-4E58-9A66-459A1AB0894F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>Email</t>
   </si>
@@ -80,9 +80,6 @@
     <t>parvathy.l@duk.ac.in</t>
   </si>
   <si>
-    <t>Keerthi@01</t>
-  </si>
-  <si>
     <t>PhoneNumber</t>
   </si>
   <si>
@@ -105,9 +102,6 @@
   </si>
   <si>
     <t>KMA</t>
-  </si>
-  <si>
-    <t>Date</t>
   </si>
   <si>
     <t>Description</t>
@@ -156,9 +150,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -205,7 +196,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -217,7 +208,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -631,7 +621,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ABD5C47-9705-4A42-9E92-0DB68C996839}">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.6640625" customWidth="1"/>
@@ -642,19 +632,18 @@
     <col min="6" max="6" width="24.44140625" customWidth="1"/>
     <col min="7" max="7" width="26.109375" customWidth="1"/>
     <col min="8" max="8" width="18.21875" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="26.109375" customWidth="1"/>
-    <col min="11" max="11" width="23.21875" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" customWidth="1"/>
-    <col min="13" max="13" width="21.5546875" customWidth="1"/>
-    <col min="14" max="14" width="19.88671875" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="16" width="17.6640625" customWidth="1"/>
-    <col min="17" max="17" width="20.6640625" customWidth="1"/>
-    <col min="18" max="18" width="24.88671875" customWidth="1"/>
+    <col min="9" max="9" width="26.109375" customWidth="1"/>
+    <col min="10" max="10" width="23.21875" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1"/>
+    <col min="12" max="12" width="21.5546875" customWidth="1"/>
+    <col min="13" max="13" width="19.88671875" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="17.6640625" customWidth="1"/>
+    <col min="16" max="16" width="20.6640625" customWidth="1"/>
+    <col min="17" max="17" width="24.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -665,28 +654,28 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" t="s">
-        <v>16</v>
-      </c>
       <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
         <v>18</v>
       </c>
-      <c r="H1" t="s">
-        <v>19</v>
-      </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J1" t="s">
         <v>23</v>
       </c>
       <c r="K1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L1" t="s">
         <v>26</v>
@@ -695,27 +684,24 @@
         <v>28</v>
       </c>
       <c r="N1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" t="s">
         <v>30</v>
       </c>
-      <c r="O1" t="s">
-        <v>31</v>
-      </c>
       <c r="P1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q1" t="s">
-        <v>35</v>
-      </c>
-      <c r="R1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>12</v>
@@ -727,42 +713,39 @@
         <v>9845678923</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="5">
-        <v>45778</v>
+      <c r="I2" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O2">
+      <c r="N2">
         <v>978906789</v>
       </c>
-      <c r="P2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="R2">
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2">
         <v>9065439087</v>
       </c>
     </row>
@@ -772,8 +755,8 @@
     <hyperlink ref="C2" r:id="rId2" xr:uid="{7FDF5D9B-4ADE-45C9-A5A8-C2D682D92ACA}"/>
     <hyperlink ref="A2" r:id="rId3" xr:uid="{DAB19B1C-BD2A-4F9E-BC0B-ED55C2149B6F}"/>
     <hyperlink ref="B2" r:id="rId4" xr:uid="{DA49A84C-6D79-4164-A119-29E5D5FC26AC}"/>
-    <hyperlink ref="N2" r:id="rId5" xr:uid="{4F758467-A264-4132-8789-579E6D532E18}"/>
-    <hyperlink ref="Q2" r:id="rId6" xr:uid="{CE372490-318A-41CA-AE30-147D93555246}"/>
+    <hyperlink ref="M2" r:id="rId5" xr:uid="{4F758467-A264-4132-8789-579E6D532E18}"/>
+    <hyperlink ref="P2" r:id="rId6" xr:uid="{CE372490-318A-41CA-AE30-147D93555246}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
